--- a/research/traditional_assets/database/data/cyprus/cyprus_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_investments_asset_management.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0178</v>
+        <v>-0.04175</v>
       </c>
       <c r="E2">
-        <v>-0.262</v>
+        <v>0.279</v>
       </c>
       <c r="G2">
-        <v>0.01603971739545542</v>
+        <v>1.129772837119381</v>
       </c>
       <c r="H2">
-        <v>0.01603971739545542</v>
+        <v>1.129772837119381</v>
       </c>
       <c r="I2">
-        <v>0.3707275157532939</v>
+        <v>0.7242629289511843</v>
       </c>
       <c r="J2">
-        <v>0.3707275157532939</v>
+        <v>0.7234220244269338</v>
       </c>
       <c r="K2">
-        <v>12.505</v>
+        <v>16.835</v>
       </c>
       <c r="L2">
-        <v>1.193908726370059</v>
+        <v>2.034195263412276</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8.65</v>
+        <v>3.481</v>
       </c>
       <c r="V2">
-        <v>0.08119016331894126</v>
+        <v>0.03178763195382985</v>
       </c>
       <c r="W2">
-        <v>0.03749191984486102</v>
+        <v>-0.03946859903381642</v>
       </c>
       <c r="X2">
-        <v>0.06803117612279301</v>
+        <v>0.1003498211161896</v>
       </c>
       <c r="Y2">
-        <v>-0.03053925627793199</v>
+        <v>-0.1398184201500061</v>
       </c>
       <c r="Z2">
-        <v>0.03077302762051105</v>
+        <v>0.02427492021775859</v>
       </c>
       <c r="AA2">
-        <v>0.01306368546664992</v>
+        <v>-0.02653631284916201</v>
       </c>
       <c r="AB2">
-        <v>0.06410322551174311</v>
+        <v>0.09900277486321483</v>
       </c>
       <c r="AC2">
-        <v>-0.05103954004509319</v>
+        <v>-0.1400322602943554</v>
       </c>
       <c r="AD2">
-        <v>15.788</v>
+        <v>7.354</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.788</v>
+        <v>7.354</v>
       </c>
       <c r="AG2">
-        <v>7.138</v>
+        <v>3.873</v>
       </c>
       <c r="AH2">
-        <v>0.1290628474265908</v>
+        <v>0.06292892471462067</v>
       </c>
       <c r="AI2">
-        <v>0.04399389190454429</v>
+        <v>0.02370468742948871</v>
       </c>
       <c r="AJ2">
-        <v>0.06279139323351923</v>
+        <v>0.03415916246990236</v>
       </c>
       <c r="AK2">
-        <v>0.02038159089481409</v>
+        <v>0.01262579339077369</v>
       </c>
       <c r="AL2">
-        <v>0.465</v>
+        <v>0.342</v>
       </c>
       <c r="AM2">
-        <v>-0.6649999999999999</v>
+        <v>0.342</v>
       </c>
       <c r="AN2">
-        <v>4.697411484677178</v>
+        <v>1.06271676300578</v>
       </c>
       <c r="AO2">
-        <v>8.350537634408603</v>
+        <v>17.52631578947369</v>
       </c>
       <c r="AP2">
-        <v>2.123772686700387</v>
+        <v>0.5596820809248555</v>
       </c>
       <c r="AQ2">
-        <v>-5.839097744360903</v>
+        <v>17.52631578947369</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLR Investment Fund Public Ltd. (CSE:CLL)</t>
+          <t>Demetra Holdings Plc (CSE:DEM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0814</v>
+        <v>0.0455</v>
+      </c>
+      <c r="E3">
+        <v>0.279</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.140243902439025</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.140243902439025</v>
       </c>
       <c r="I3">
-        <v>0.7853403141361256</v>
+        <v>0.8365853658536586</v>
       </c>
       <c r="J3">
-        <v>0.7853403141361256</v>
+        <v>0.8336714168265279</v>
       </c>
       <c r="K3">
-        <v>-0.365</v>
+        <v>17.8</v>
       </c>
       <c r="L3">
-        <v>-0.4777486910994764</v>
+        <v>2.170731707317073</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,73 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.72</v>
+        <v>0.948</v>
       </c>
       <c r="V3">
-        <v>1.508771929824561</v>
+        <v>0.009395441030723487</v>
       </c>
       <c r="W3">
-        <v>-0.1147798742138365</v>
+        <v>0.05606299212598426</v>
       </c>
       <c r="X3">
-        <v>0.09337678817023638</v>
+        <v>0.1003498211161896</v>
       </c>
       <c r="Y3">
-        <v>-0.2081566623840728</v>
+        <v>-0.04428682899020539</v>
       </c>
       <c r="Z3">
-        <v>0.359868111163448</v>
+        <v>0.02509871139542714</v>
       </c>
       <c r="AA3">
-        <v>0.2826189354686764</v>
+        <v>0.02092407828954586</v>
       </c>
       <c r="AB3">
-        <v>0.07251779604115136</v>
+        <v>0.09900277486321483</v>
       </c>
       <c r="AC3">
-        <v>0.2101011394275251</v>
+        <v>-0.07807869657366898</v>
       </c>
       <c r="AD3">
-        <v>0.888</v>
+        <v>6.55</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.888</v>
+        <v>6.55</v>
       </c>
       <c r="AG3">
-        <v>-0.832</v>
+        <v>5.602</v>
       </c>
       <c r="AH3">
-        <v>0.4378698224852071</v>
+        <v>0.06095858538855281</v>
       </c>
       <c r="AI3">
-        <v>0.2295760082730093</v>
+        <v>0.02262130892764634</v>
       </c>
       <c r="AJ3">
-        <v>-2.701298701298702</v>
+        <v>0.05259995117462583</v>
       </c>
       <c r="AK3">
-        <v>-0.3873370577281192</v>
+        <v>0.01941081489386768</v>
       </c>
       <c r="AL3">
-        <v>0.047</v>
+        <v>0.293</v>
       </c>
       <c r="AM3">
-        <v>0.047</v>
+        <v>0.293</v>
+      </c>
+      <c r="AN3">
+        <v>0.9465317919075145</v>
       </c>
       <c r="AO3">
-        <v>12.76595744680851</v>
+        <v>23.41296928327645</v>
+      </c>
+      <c r="AP3">
+        <v>0.8095375722543353</v>
       </c>
       <c r="AQ3">
-        <v>12.76595744680851</v>
+        <v>23.41296928327645</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Demetra Holdings Plc (CSE:DEM)</t>
+          <t>CLR Investment Fund Public Ltd. (CSE:CLL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,23 +849,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.129</v>
+      </c>
       <c r="G4">
-        <v>0.1778140293637847</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1778140293637847</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.6786296900489397</v>
+        <v>-0.75</v>
       </c>
       <c r="J4">
-        <v>0.6786296900489397</v>
+        <v>-0.75</v>
       </c>
       <c r="K4">
-        <v>11.6</v>
+        <v>-0.148</v>
       </c>
       <c r="L4">
-        <v>1.892332789559543</v>
+        <v>-1.947368421052632</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,7 +877,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -874,79 +886,73 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.69</v>
+        <v>2.33</v>
       </c>
       <c r="V4">
-        <v>0.05983175604626709</v>
+        <v>3.033854166666667</v>
       </c>
       <c r="W4">
-        <v>0.03749191984486102</v>
+        <v>-0.04966442953020134</v>
       </c>
       <c r="X4">
-        <v>0.06803117612279301</v>
+        <v>0.1503918576827576</v>
       </c>
       <c r="Y4">
-        <v>-0.03053925627793199</v>
+        <v>-0.2000562872129589</v>
       </c>
       <c r="Z4">
-        <v>0.01925009420927019</v>
+        <v>0.03538175046554935</v>
       </c>
       <c r="AA4">
-        <v>0.01306368546664992</v>
+        <v>-0.02653631284916201</v>
       </c>
       <c r="AB4">
-        <v>0.06410322551174311</v>
+        <v>0.1134959474451934</v>
       </c>
       <c r="AC4">
-        <v>-0.05103954004509319</v>
+        <v>-0.1400322602943554</v>
       </c>
       <c r="AD4">
-        <v>14.9</v>
+        <v>0.804</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14.9</v>
+        <v>0.804</v>
       </c>
       <c r="AG4">
-        <v>9.210000000000001</v>
+        <v>-1.526</v>
       </c>
       <c r="AH4">
-        <v>0.1354545454545455</v>
+        <v>0.5114503816793893</v>
       </c>
       <c r="AI4">
-        <v>0.04482551143200963</v>
+        <v>0.2448233861144946</v>
       </c>
       <c r="AJ4">
-        <v>0.08829450675870003</v>
+        <v>2.013192612137203</v>
       </c>
       <c r="AK4">
-        <v>0.02819013804291268</v>
+        <v>-1.59958071278826</v>
       </c>
       <c r="AL4">
-        <v>0.418</v>
+        <v>0.042</v>
       </c>
       <c r="AM4">
-        <v>0.418</v>
-      </c>
-      <c r="AN4">
-        <v>3.522458628841607</v>
+        <v>0.042</v>
       </c>
       <c r="AO4">
-        <v>9.952153110047847</v>
-      </c>
-      <c r="AP4">
-        <v>2.177304964539007</v>
+        <v>-1.357142857142857</v>
       </c>
       <c r="AQ4">
-        <v>9.952153110047847</v>
+        <v>-1.357142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Argo Group Limited (AIM:ARGO)</t>
+          <t>Interfund Investments Plc. (CSE:INF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,29 +971,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.117</v>
-      </c>
-      <c r="E5">
-        <v>-0.262</v>
-      </c>
-      <c r="G5">
-        <v>-0.2575418994413408</v>
-      </c>
-      <c r="H5">
-        <v>-0.2575418994413408</v>
-      </c>
-      <c r="I5">
-        <v>-0.2449720670391062</v>
-      </c>
-      <c r="J5">
-        <v>-0.2449720670391062</v>
-      </c>
       <c r="K5">
-        <v>1.27</v>
-      </c>
-      <c r="L5">
-        <v>0.3547486033519553</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,7 +981,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,37 +990,37 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.24</v>
+        <v>0.203</v>
       </c>
       <c r="V5">
-        <v>0.1203883495145631</v>
+        <v>0.02589285714285714</v>
       </c>
       <c r="W5">
-        <v>0.05934579439252337</v>
+        <v>-0.03946859903381642</v>
       </c>
       <c r="X5">
-        <v>0.06164957668965544</v>
+        <v>0.09704162195063393</v>
       </c>
       <c r="Y5">
-        <v>-0.002303782297132073</v>
+        <v>-0.1365102209844503</v>
       </c>
       <c r="Z5">
-        <v>0.1808080808080808</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.0442929292929293</v>
+        <v>-0.06702568351284177</v>
       </c>
       <c r="AB5">
-        <v>0.06164957668965544</v>
+        <v>0.09704162195063393</v>
       </c>
       <c r="AC5">
-        <v>-0.1059425059825847</v>
+        <v>-0.1640673054634757</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1047,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-1.24</v>
+        <v>-0.203</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1056,25 +1041,22 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1368653421633554</v>
+        <v>-0.02658111824014666</v>
       </c>
       <c r="AK5">
-        <v>-0.05805243445692883</v>
+        <v>-0.01180438448566611</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM5">
-        <v>-1.13</v>
-      </c>
-      <c r="AN5">
-        <v>-0</v>
-      </c>
-      <c r="AP5">
-        <v>1.42692750287687</v>
+        <v>0.007</v>
+      </c>
+      <c r="AO5">
+        <v>-115.5714285714286</v>
       </c>
       <c r="AQ5">
-        <v>0.7761061946902655</v>
+        <v>-115.5714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cyprus/cyprus_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.04175</v>
-      </c>
-      <c r="E2">
-        <v>0.279</v>
+        <v>0.388</v>
       </c>
       <c r="G2">
-        <v>1.129772837119381</v>
+        <v>0.2372614878868005</v>
       </c>
       <c r="H2">
-        <v>1.129772837119381</v>
+        <v>0.2372614878868005</v>
       </c>
       <c r="I2">
-        <v>0.7242629289511843</v>
+        <v>0.8531408561423569</v>
       </c>
       <c r="J2">
-        <v>0.7234220244269338</v>
+        <v>0.8525648584591037</v>
       </c>
       <c r="K2">
-        <v>16.835</v>
+        <v>52.474</v>
       </c>
       <c r="L2">
-        <v>2.034195263412276</v>
+        <v>3.750017866075895</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.481</v>
+        <v>2.432</v>
       </c>
       <c r="V2">
-        <v>0.03178763195382985</v>
+        <v>0.01444515059901046</v>
       </c>
       <c r="W2">
-        <v>-0.03946859903381642</v>
+        <v>0.1418088217375411</v>
       </c>
       <c r="X2">
-        <v>0.1003498211161896</v>
+        <v>0.0869668654144487</v>
       </c>
       <c r="Y2">
-        <v>-0.1398184201500061</v>
+        <v>0.05484195632309241</v>
       </c>
       <c r="Z2">
-        <v>0.02427492021775859</v>
+        <v>0.04561650578804445</v>
       </c>
       <c r="AA2">
-        <v>-0.02653631284916201</v>
+        <v>0.07164180300317637</v>
       </c>
       <c r="AB2">
-        <v>0.09900277486321483</v>
+        <v>0.0916849769053715</v>
       </c>
       <c r="AC2">
-        <v>-0.1400322602943554</v>
+        <v>-0.005351530453363059</v>
       </c>
       <c r="AD2">
-        <v>7.354</v>
+        <v>7.777</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.354</v>
+        <v>7.777</v>
       </c>
       <c r="AG2">
-        <v>3.873</v>
+        <v>5.345000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.06292892471462067</v>
+        <v>0.0441528801280814</v>
       </c>
       <c r="AI2">
-        <v>0.02370468742948871</v>
+        <v>0.01988280471030981</v>
       </c>
       <c r="AJ2">
-        <v>0.03415916246990236</v>
+        <v>0.0307703821399376</v>
       </c>
       <c r="AK2">
-        <v>0.01262579339077369</v>
+        <v>0.01375061099534357</v>
       </c>
       <c r="AL2">
-        <v>0.342</v>
+        <v>0.529</v>
       </c>
       <c r="AM2">
-        <v>0.342</v>
+        <v>0.529</v>
       </c>
       <c r="AN2">
-        <v>1.06271676300578</v>
+        <v>0.7847628657921292</v>
       </c>
       <c r="AO2">
-        <v>17.52631578947369</v>
+        <v>22.56710775047259</v>
       </c>
       <c r="AP2">
-        <v>0.5596820809248555</v>
+        <v>0.5393541876892028</v>
       </c>
       <c r="AQ2">
-        <v>17.52631578947369</v>
+        <v>22.56710775047259</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Demetra Holdings Plc (CSE:DEM)</t>
+          <t>CLR Investment Fund Public Ltd. (CSE:CLL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,28 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0455</v>
-      </c>
-      <c r="E3">
-        <v>0.279</v>
+        <v>-0.133</v>
       </c>
       <c r="G3">
-        <v>1.140243902439025</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1.140243902439025</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8365853658536586</v>
+        <v>0.5593220338983051</v>
       </c>
       <c r="J3">
-        <v>0.8336714168265279</v>
+        <v>0.5593220338983051</v>
       </c>
       <c r="K3">
-        <v>17.8</v>
+        <v>0.167</v>
       </c>
       <c r="L3">
-        <v>2.170731707317073</v>
+        <v>0.4043583535108959</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +758,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.948</v>
+        <v>1.54</v>
       </c>
       <c r="V3">
-        <v>0.009395441030723487</v>
+        <v>1.387387387387387</v>
       </c>
       <c r="W3">
-        <v>0.05606299212598426</v>
+        <v>0.06733870967741935</v>
       </c>
       <c r="X3">
-        <v>0.1003498211161896</v>
+        <v>0.09593611843637938</v>
       </c>
       <c r="Y3">
-        <v>-0.04428682899020539</v>
+        <v>-0.02859740875896002</v>
       </c>
       <c r="Z3">
-        <v>0.02509871139542714</v>
+        <v>0.4329140461215934</v>
       </c>
       <c r="AA3">
-        <v>0.02092407828954586</v>
+        <v>0.2421383647798743</v>
       </c>
       <c r="AB3">
-        <v>0.09900277486321483</v>
+        <v>0.1072690455154382</v>
       </c>
       <c r="AC3">
-        <v>-0.07807869657366898</v>
+        <v>0.1348693192644361</v>
       </c>
       <c r="AD3">
-        <v>6.55</v>
+        <v>0.652</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.55</v>
+        <v>0.652</v>
       </c>
       <c r="AG3">
-        <v>5.602</v>
+        <v>-0.888</v>
       </c>
       <c r="AH3">
-        <v>0.06095858538855281</v>
+        <v>0.3700340522133939</v>
       </c>
       <c r="AI3">
-        <v>0.02262130892764634</v>
+        <v>0.1910902696365768</v>
       </c>
       <c r="AJ3">
-        <v>0.05259995117462583</v>
+        <v>-3.999999999999999</v>
       </c>
       <c r="AK3">
-        <v>0.01941081489386768</v>
+        <v>-0.4743589743589744</v>
       </c>
       <c r="AL3">
-        <v>0.293</v>
+        <v>0.037</v>
       </c>
       <c r="AM3">
-        <v>0.293</v>
-      </c>
-      <c r="AN3">
-        <v>0.9465317919075145</v>
+        <v>0.037</v>
       </c>
       <c r="AO3">
-        <v>23.41296928327645</v>
-      </c>
-      <c r="AP3">
-        <v>0.8095375722543353</v>
+        <v>6.243243243243244</v>
       </c>
       <c r="AQ3">
-        <v>23.41296928327645</v>
+        <v>6.243243243243244</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLR Investment Fund Public Ltd. (CSE:CLL)</t>
+          <t>Interfund Investments Plc. (CSE:INF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,7 +838,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.129</v>
+        <v>0.762</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,16 +847,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.75</v>
+        <v>0.8623853211009174</v>
       </c>
       <c r="J4">
-        <v>-0.75</v>
+        <v>0.8619140722915727</v>
       </c>
       <c r="K4">
-        <v>-0.148</v>
+        <v>1.83</v>
       </c>
       <c r="L4">
-        <v>-1.947368421052632</v>
+        <v>0.8394495412844036</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,7 +865,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,73 +874,73 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.33</v>
+        <v>0.074</v>
       </c>
       <c r="V4">
-        <v>3.033854166666667</v>
+        <v>0.009284818067754077</v>
       </c>
       <c r="W4">
-        <v>-0.04966442953020134</v>
+        <v>0.1051724137931035</v>
       </c>
       <c r="X4">
-        <v>0.1503918576827576</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="Y4">
-        <v>-0.2000562872129589</v>
+        <v>0.02863299608148126</v>
       </c>
       <c r="Z4">
-        <v>0.03538175046554935</v>
+        <v>0.1267662964470547</v>
       </c>
       <c r="AA4">
-        <v>-0.02653631284916201</v>
+        <v>0.1092616548000016</v>
       </c>
       <c r="AB4">
-        <v>0.1134959474451934</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="AC4">
-        <v>-0.1400322602943554</v>
+        <v>0.03272223708837944</v>
       </c>
       <c r="AD4">
-        <v>0.804</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.804</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.526</v>
+        <v>-0.074</v>
       </c>
       <c r="AH4">
-        <v>0.5114503816793893</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.2448233861144946</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>2.013192612137203</v>
+        <v>-0.009371833839918946</v>
       </c>
       <c r="AK4">
-        <v>-1.59958071278826</v>
+        <v>-0.002921898444286504</v>
       </c>
       <c r="AL4">
-        <v>0.042</v>
+        <v>0.007</v>
       </c>
       <c r="AM4">
-        <v>0.042</v>
+        <v>0.007</v>
       </c>
       <c r="AO4">
-        <v>-1.357142857142857</v>
+        <v>268.5714285714286</v>
       </c>
       <c r="AQ4">
-        <v>-1.357142857142857</v>
+        <v>268.5714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Interfund Investments Plc. (CSE:INF)</t>
+          <t>Demetra Holdings Plc (CSE:DEM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,8 +959,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.388</v>
+      </c>
+      <c r="G5">
+        <v>0.2912280701754386</v>
+      </c>
+      <c r="H5">
+        <v>0.2912280701754386</v>
+      </c>
+      <c r="I5">
+        <v>0.863157894736842</v>
+      </c>
+      <c r="J5">
+        <v>0.8612985229873101</v>
+      </c>
       <c r="K5">
-        <v>-0.8169999999999999</v>
+        <v>50.5</v>
+      </c>
+      <c r="L5">
+        <v>4.429824561403509</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -981,7 +987,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -990,73 +996,162 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.203</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="V5">
-        <v>0.02589285714285714</v>
+        <v>0.005138190954773869</v>
       </c>
       <c r="W5">
-        <v>-0.03946859903381642</v>
+        <v>0.1784452296819788</v>
       </c>
       <c r="X5">
-        <v>0.09704162195063393</v>
+        <v>0.07799761239251804</v>
       </c>
       <c r="Y5">
-        <v>-0.1365102209844503</v>
+        <v>0.1004476172894607</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.03950076576045904</v>
       </c>
       <c r="AA5">
-        <v>-0.06702568351284177</v>
+        <v>0.03402195120635108</v>
       </c>
       <c r="AB5">
-        <v>0.09704162195063393</v>
+        <v>0.07744724920145664</v>
       </c>
       <c r="AC5">
-        <v>-0.1640673054634757</v>
+        <v>-0.04342529799510556</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="AG5">
-        <v>-0.203</v>
+        <v>6.212000000000001</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.04229080190098057</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.01940220241216571</v>
       </c>
       <c r="AJ5">
-        <v>-0.02658111824014666</v>
+        <v>0.03755471187096463</v>
       </c>
       <c r="AK5">
-        <v>-0.01180438448566611</v>
+        <v>0.01718338533713957</v>
       </c>
       <c r="AL5">
-        <v>0.007</v>
+        <v>0.485</v>
       </c>
       <c r="AM5">
-        <v>0.007</v>
+        <v>0.485</v>
+      </c>
+      <c r="AN5">
+        <v>0.7093844601412714</v>
       </c>
       <c r="AO5">
-        <v>-115.5714285714286</v>
+        <v>20.28865979381443</v>
+      </c>
+      <c r="AP5">
+        <v>0.6268415741675076</v>
       </c>
       <c r="AQ5">
-        <v>-115.5714285714286</v>
+        <v>20.28865979381443</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CPI Holdings Public Limited (CSE:CPIH)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-0.023</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.3432835820895522</v>
+      </c>
+      <c r="X6">
+        <v>0.115268912739753</v>
+      </c>
+      <c r="Y6">
+        <v>0.2280146693497992</v>
+      </c>
+      <c r="AB6">
+        <v>0.1059227046092864</v>
+      </c>
+      <c r="AD6">
+        <v>0.095</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0.095</v>
+      </c>
+      <c r="AG6">
+        <v>0.095</v>
+      </c>
+      <c r="AH6">
+        <v>0.5397727272727273</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5397727272727273</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
